--- a/Config/Luban/Datas/#game.buff.xlsx
+++ b/Config/Luban/Datas/#game.buff.xlsx
@@ -510,12 +510,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="5"/>
-    <col width="14" customWidth="1" min="6" max="15"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="5"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="15"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -541,22 +545,17 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>effects#format=json</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>effects#format=json</t>
+          <t>cost</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>triggerConditions#format=json</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>cost</t>
+          <t>weight</t>
         </is>
       </c>
     </row>
@@ -583,20 +582,15 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>array,array,int</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>array,array,int</t>
-        </is>
-      </c>
       <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>array,array,int</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -614,7 +608,6 @@
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4" ht="48" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
@@ -629,32 +622,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>BUFF标题</t>
+          <t>BUFF名字</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>BUFF内容</t>
+          <t>BUFF介绍</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>TYPE</t>
+          <t>BUFF对属性的修改，格式[[属性ID,值]]</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>BUFF生效时的属性修改，格式[[属性ID,值]]</t>
+          <t>BUFF花费</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>BUFF触发条件，格式[[属性ID,阈值]]；阈值语义由运行时解释</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Cost</t>
+          <t>BUFF权重</t>
         </is>
       </c>
     </row>
@@ -670,24 +658,19 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>提高月愿望单增长，并少量追加当前愿望单。</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+          <t>提高周愿望增长，并少量追加当前愿望单。</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>[[1004,500],[1009,1]]</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>[[1009,5]]</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="n">
+      <c r="F5" s="2" t="n">
         <v>15</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="6" ht="28.5" customHeight="1">
@@ -705,21 +688,16 @@
           <t>围绕愿望单和质量分的整数属性调整。</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>[[1009,1],[1010,2]]</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>[[1009,3],[1010,6]]</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n">
+      <c r="F6" s="2" t="n">
         <v>25</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="7" ht="28.5" customHeight="1">
@@ -734,24 +712,19 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>同时调整月愿望单增长、画面、氛围、愿望单、质量分和Bug。</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+          <t>同时调整周愿望增长、画面、氛围、愿望单、质量分和Bug。</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>[[1004,300],[1006,50],[1007,10],[1009,1],[1010,2],[1005,2]]</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>[[1009,4],[1010,8],[1005,12]]</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n">
+      <c r="F7" s="2" t="n">
         <v>40</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Luban/Datas/#game.buff.xlsx
+++ b/Config/Luban/Datas/#game.buff.xlsx
@@ -510,14 +510,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="5"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="15"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
@@ -545,15 +545,20 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>effects#format=json</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>cost</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
@@ -582,15 +587,20 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>array,array,int</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -608,6 +618,7 @@
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4" ht="48" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
@@ -632,15 +643,20 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>BUFF图标路径，留空表示暂无图标</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>BUFF对属性的修改，格式[[属性ID,值]]</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>BUFF花费</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>BUFF权重</t>
         </is>
@@ -661,15 +677,16 @@
           <t>提高周愿望增长，并少量追加当前愿望单。</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>[[1004,500],[1009,1]]</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="G5" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="H5" s="2" t="n">
         <v>100</v>
       </c>
     </row>
@@ -688,15 +705,16 @@
           <t>围绕愿望单和质量分的整数属性调整。</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>[[1009,1],[1010,2]]</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="G6" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="H6" s="2" t="n">
         <v>100</v>
       </c>
     </row>
@@ -715,16 +733,297 @@
           <t>同时调整周愿望增长、画面、氛围、愿望单、质量分和Bug。</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>[[1004,300],[1006,50],[1007,10],[1009,1],[1010,2],[1005,2]]</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="G7" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="H7" s="2" t="n">
         <v>100</v>
+      </c>
+    </row>
+    <row r="8" ht="28.5" customHeight="1">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="2" t="n">
+        <v>2004</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>测试BUFF-程序加速</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>提高程序房间行动收益，用于测试房间成长类Buff。</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>[[1017,1],[1011,1],[1012,2]]</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" ht="28.5" customHeight="1">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="2" t="n">
+        <v>2005</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>测试BUFF-美术强化</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>提高画面表现，并追加每周画面变化量。</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>[[1018,1],[1006,20],[1029,5]]</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" ht="28.5" customHeight="1">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="2" t="n">
+        <v>2006</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>测试BUFF-音效打磨</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>提高氛围表现，并追加每周氛围变化量。</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>[[1019,1],[1007,20],[1030,5]]</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" ht="28.5" customHeight="1">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="2" t="n">
+        <v>2007</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>测试BUFF-修Bug冲刺</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>降低当前Bug并改善每周Bug变化，少量提升质量。</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>[[1005,-5],[1028,-1],[1010,1]]</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" ht="28.5" customHeight="1">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="2" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>测试BUFF-宣传预热</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>直接增加愿望单，并提高愿望单增长百分比。</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>[[1009,3],[1024,10]]</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" ht="28.5" customHeight="1">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>测试BUFF-稳定版本</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>兼顾降低Bug、提升质量和提高周愿望增长。</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>[[1005,-2],[1010,3],[1004,100]]</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" ht="28.5" customHeight="1">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>测试BUFF-灵感爆发</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>大幅提升画面和氛围，但额外引入少量Bug。</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>[[1006,30],[1007,30],[1005,3]]</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" ht="28.5" customHeight="1">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="2" t="n">
+        <v>2011</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>测试BUFF-月度补给</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>返还少量金币并追加愿望单，用于测试金币属性修改。</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>[[1008,50],[1009,1]]</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" ht="28.5" customHeight="1">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>测试BUFF-专注迭代</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>增加基础周行动力，并提高周愿望增长和三房间奖励。</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>[[1001,1],[1004,150],[1026,5]]</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" ht="28.5" customHeight="1">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>测试BUFF-口碑发酵</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>提高愿望单数量、画面达标奖励和增长百分比。</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>[[1009,5],[1025,10],[1024,5]]</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Luban/Datas/#game.buff.xlsx
+++ b/Config/Luban/Datas/#game.buff.xlsx
@@ -515,11 +515,13 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="5"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="15"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="15"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -540,12 +542,12 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>brief</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>content</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>icon</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
@@ -638,12 +640,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>BUFF介绍</t>
+          <t>BUFF简述</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>BUFF图标路径，留空表示暂无图标</t>
+          <t>BUFF效果介绍</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -669,22 +671,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>测试BUFF-愿望成长</t>
+          <t>画笔</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>提高周愿望增长，并少量追加当前愿望单。</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
+          <t>美术房里的主力画刷，双倍蘸料，双倍细节。</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>每回合美术房选择消耗两点数选项，愿望单+50000</t>
+        </is>
+      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>[[1004,500],[1009,1]]</t>
+          <t>[[1014,50000]]</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>100</v>
@@ -697,25 +703,29 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>测试BUFF-质量目标</t>
+          <t>速写便签</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>围绕愿望单和质量分的整数属性调整。</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
+          <t>随手贴在美术墙上的日常草稿，积攒灵感。</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>每回合在美术房消耗行动点数，愿望单+30000</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>[[1009,1],[1010,2]]</t>
+          <t>[[1018,30000]]</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" ht="28.5" customHeight="1">
@@ -725,22 +735,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>测试BUFF-综合成长</t>
+          <t>机械键盘</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>同时调整周愿望增长、画面、氛围、愿望单、质量分和Bug。</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
+          <t>咔哒作响的机械键盘，日常敲击累积进度。</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>每回合程序房选择消耗两点数选项，愿望单+40000</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>[[1004,300],[1006,50],[1007,10],[1009,1],[1010,2],[1005,2]]</t>
+          <t>[[1012,40000]]</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>100</v>
@@ -753,25 +767,29 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>测试BUFF-程序加速</t>
+          <t>5090算力加速</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>提高程序房间行动收益，用于测试房间成长类Buff。</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
+          <t>程序房里的顶级显卡，双倍算力暴力重构代码。</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>每回合在程序房消耗行动点数，愿望单+30000</t>
+        </is>
+      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>[[1017,1],[1011,1],[1012,2]]</t>
+          <t>[[1017,30000]]</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" ht="28.5" customHeight="1">
@@ -781,25 +799,29 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>测试BUFF-美术强化</t>
+          <t>调音台</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>提高画面表现，并追加每周画面变化量。</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr"/>
+          <t>音效房的核心控制台，双倍推拉打磨每条音轨。</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>每回合音效房选择消耗两点数选项，愿望单+50000</t>
+        </is>
+      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>[[1018,1],[1006,20],[1029,5]]</t>
+          <t>[[1016,50000]]</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" ht="28.5" customHeight="1">
@@ -809,25 +831,29 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>测试BUFF-音效打磨</t>
+          <t>贝斯</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>提高氛围表现，并追加每周氛围变化量。</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr"/>
+          <t>偶尔弹两下，节奏素材也算没白录。</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>每回合在音效房消耗行动点数，愿望单+20000</t>
+        </is>
+      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>[[1019,1],[1007,20],[1030,5]]</t>
+          <t>[[1019,20000]]</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>90</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" ht="28.5" customHeight="1">
@@ -837,25 +863,29 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>测试BUFF-修Bug冲刺</t>
+          <t>能量饮料</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>降低当前Bug并改善每周Bug变化，少量提升质量。</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr"/>
+          <t>冰镇能量饮料，连续两回合不换房间，工作效率翻倍。</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>连续两回合在同一房间消耗点数，愿望单+80000</t>
+        </is>
+      </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>[[1005,-5],[1028,-1],[1010,1]]</t>
+          <t>[[1020,80000]]</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" ht="28.5" customHeight="1">
@@ -865,25 +895,29 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>测试BUFF-宣传预热</t>
+          <t>招财猫</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>直接增加愿望单，并提高愿望单增长百分比。</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
+          <t>工作室的原生猫咪，偶尔带来翻倍的好运气。</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>每回合开始，有50%概率获得愿望单×2</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>[[1009,3],[1024,10]]</t>
+          <t>[[1021,2]]</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" ht="28.5" customHeight="1">
@@ -893,25 +927,29 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>测试BUFF-稳定版本</t>
+          <t>里程碑奖杯</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>兼顾降低Bug、提升质量和提高周愿望增长。</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
+          <t>每过三个回合，项目节点奖金到账。</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>第3、6、9回合结束时，各获得愿望单+150000</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>[[1005,-2],[1010,3],[1004,100]]</t>
+          <t>[[1022,150000]]</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" ht="28.5" customHeight="1">
@@ -921,25 +959,29 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>测试BUFF-灵感爆发</t>
+          <t>塔罗水晶球</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>大幅提升画面和氛围，但额外引入少量Bug。</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
+          <t>摊开牌阵，水晶球里隐约映出项目命运——BUG越少，水晶球越亮。</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>BUG低于40时，每回合愿望单+100000</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>[[1006,30],[1007,30],[1005,3]]</t>
+          <t>[[1023,100000]]</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" ht="28.5" customHeight="1">
@@ -949,25 +991,29 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>测试BUFF-月度补给</t>
+          <t>美术资源展板</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>返还少量金币并追加愿望单，用于测试金币属性修改。</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr"/>
+          <t>画面值堆满时，挂出的高质量美术素材吸引更多目光。</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>画面值高于60时，每回合愿望单增长量提高50%。</t>
+        </is>
+      </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>[[1008,50],[1009,1]]</t>
+          <t>[[1025,50]]</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" ht="28.5" customHeight="1">
@@ -977,22 +1023,26 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>测试BUFF-专注迭代</t>
+          <t>全能咖啡机</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>增加基础周行动力，并提高周愿望增长和三房间奖励。</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr"/>
+          <t>按下咖啡机，全体瞬间清醒，美术、程序、音效三线暴走。</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>同一回合，在三个房间都消耗行动点，愿望单+200000</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>[[1001,1],[1004,150],[1026,5]]</t>
+          <t>[[1026,200000]]</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>55</v>
@@ -1005,22 +1055,26 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>测试BUFF-口碑发酵</t>
+          <t>外包团队</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>提高愿望单数量、画面达标奖励和增长百分比。</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr"/>
+          <t>聘请业内顶尖的神秘开发大佬，流程规范，交付稳定，品质有保障。</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>每回合bug值额外降低2点，愿望单增加1000000</t>
+        </is>
+      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>[[1009,5],[1025,10],[1024,5]]</t>
+          <t>[[1028,-2],[1009,1000000]]</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>45</v>

--- a/Config/Luban/Datas/#game.buff.xlsx
+++ b/Config/Luban/Datas/#game.buff.xlsx
@@ -1512,7 +1512,7 @@
         <v>43</v>
       </c>
       <c r="G10" s="2">
-        <v>14</v>
+        <v>40000</v>
       </c>
       <c r="H10" s="2">
         <v>125</v>
@@ -1536,7 +1536,7 @@
         <v>47</v>
       </c>
       <c r="G11" s="2">
-        <v>28</v>
+        <v>55000</v>
       </c>
       <c r="H11" s="2">
         <v>80</v>
@@ -1560,7 +1560,7 @@
         <v>51</v>
       </c>
       <c r="G12" s="2">
-        <v>30</v>
+        <v>90000</v>
       </c>
       <c r="H12" s="2">
         <v>70</v>
@@ -1584,7 +1584,7 @@
         <v>55</v>
       </c>
       <c r="G13" s="2">
-        <v>35</v>
+        <v>70000</v>
       </c>
       <c r="H13" s="2">
         <v>65</v>
@@ -1608,7 +1608,7 @@
         <v>59</v>
       </c>
       <c r="G14" s="2">
-        <v>32</v>
+        <v>65000</v>
       </c>
       <c r="H14" s="2">
         <v>75</v>
@@ -1632,7 +1632,7 @@
         <v>63</v>
       </c>
       <c r="G15" s="2">
-        <v>26</v>
+        <v>80000</v>
       </c>
       <c r="H15" s="2">
         <v>85</v>
@@ -1656,7 +1656,7 @@
         <v>67</v>
       </c>
       <c r="G16" s="2">
-        <v>40</v>
+        <v>80000</v>
       </c>
       <c r="H16" s="2">
         <v>55</v>
@@ -1680,7 +1680,7 @@
         <v>71</v>
       </c>
       <c r="G17" s="2">
-        <v>45</v>
+        <v>95000</v>
       </c>
       <c r="H17" s="2">
         <v>45</v>
